--- a/ebegu-server/src/main/resources/reporting/Zahlungen_FR.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_FR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projekte\kibon-app\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F465DB39-BF48-4340-BC2E-FF47267C107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A1829-8AC6-4B44-BE78-6C52D3E1A31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -116,9 +116,6 @@
     <t>{kindNachname} {kindVorname}</t>
   </si>
   <si>
-    <t>Spaltenbeschriftungen</t>
-  </si>
-  <si>
     <t>Filter</t>
   </si>
   <si>
@@ -332,12 +329,6 @@
     <t xml:space="preserve">A partir de </t>
   </si>
   <si>
-    <t>(Alle)</t>
-  </si>
-  <si>
-    <t>#WERT!</t>
-  </si>
-  <si>
     <t>Summe von Montant en francs</t>
   </si>
   <si>
@@ -345,6 +336,15 @@
   </si>
   <si>
     <t>Cellule complétée</t>
+  </si>
+  <si>
+    <t>Étiquettes de colonnes</t>
+  </si>
+  <si>
+    <t>#VALEUR!</t>
+  </si>
+  <si>
+    <t>(Tous)</t>
   </si>
 </sst>
 </file>
@@ -584,16 +584,16 @@
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Neutral 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pivot Table Category" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Pivot Table Corner" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Pivot Table Field" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Pivot Table Result" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Pivot Table Title" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="Pivot Table Value" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="24">
     <dxf>
       <alignment wrapText="1" indent="0"/>
     </dxf>
@@ -617,30 +617,6 @@
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -776,7 +752,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kafader Simon" refreshedDate="46027.606349189817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{19CCD4CE-71BA-456C-AC09-85819591646C}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Kafader Simon" refreshedDate="46027.606349189817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{19CCD4CE-71BA-456C-AC09-85819591646C}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A12:V1048576" sheet="Data"/>
   </cacheSource>
@@ -937,7 +913,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8E51875-8A88-48FE-A37D-3A132351B8AB}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="filtrage">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8E51875-8A88-48FE-A37D-3A132351B8AB}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="filtrage">
   <location ref="A8:C16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
@@ -1059,28 +1035,28 @@
     <dataField name="Summe von Montant en francs" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="31">
+    <format dxfId="23">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="22">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="21">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="20">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="18">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="17">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1094,7 +1070,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{182DBE84-424D-47FB-9F75-85364042AE94}" name="DataPilot1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{182DBE84-424D-47FB-9F75-85364042AE94}" name="DataPilot1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A9:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
@@ -1197,13 +1173,13 @@
     <dataField name="Summe von Montant en francs" fld="14" baseField="3" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="23">
+    <format dxfId="15">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="14">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1217,9 +1193,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1257,7 +1233,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1363,7 +1339,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1514,62 +1490,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="22" customWidth="1"/>
-    <col min="3" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="22" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="22" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="22" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" style="22" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="4"/>
-    <col min="17" max="17" width="18.85546875" style="4" customWidth="1"/>
-    <col min="18" max="19" width="23.28515625" customWidth="1"/>
-    <col min="20" max="20" width="21.140625" customWidth="1"/>
-    <col min="21" max="21" width="44.28515625" customWidth="1"/>
-    <col min="22" max="22" width="47.5703125" style="4" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="22" customWidth="1"/>
+    <col min="3" max="4" width="21.1640625" customWidth="1"/>
+    <col min="5" max="5" width="34.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="22" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="22" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="22" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="22" customWidth="1"/>
+    <col min="14" max="14" width="19.5" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.5" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="4"/>
+    <col min="17" max="17" width="18.83203125" style="4" customWidth="1"/>
+    <col min="18" max="19" width="23.33203125" customWidth="1"/>
+    <col min="20" max="20" width="21.1640625" customWidth="1"/>
+    <col min="21" max="21" width="44.33203125" customWidth="1"/>
+    <col min="22" max="22" width="47.5" style="4" customWidth="1"/>
+    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="17"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="B3" s="18"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1577,99 +1553,99 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="11" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="C12" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="J12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="K12" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="L12" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="L12" s="20" t="s">
+      <c r="M12" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="M12" s="20" t="s">
+      <c r="N12" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="O12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="P12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="Q12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="R12" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="R12" s="10" t="s">
+      <c r="S12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S12" s="10" t="s">
-        <v>44</v>
-      </c>
       <c r="T12" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="U12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="V12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="V12" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>5</v>
       </c>
@@ -1753,12 +1729,12 @@
     <sortCondition ref="J13"/>
   </sortState>
   <conditionalFormatting sqref="A13:P13 R13:W13">
-    <cfRule type="expression" dxfId="20" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>$N13="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$M13="X"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1770,99 +1746,99 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" style="26" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="26" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" style="26" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="26"/>
+    <col min="1" max="1" width="26.83203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" style="26" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
       <c r="D1" s="30"/>
       <c r="E1" s="33"/>
     </row>
-    <row r="2" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
       <c r="E2" s="33"/>
     </row>
-    <row r="3" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="33"/>
     </row>
-    <row r="4" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
       <c r="E4" s="33"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="31"/>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E7"/>
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>23</v>
-      </c>
       <c r="D8"/>
     </row>
-    <row r="9" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>48</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>49</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="32" t="s">
         <v>7</v>
       </c>
@@ -1873,7 +1849,7 @@
       <c r="F10"/>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="32" t="s">
         <v>8</v>
       </c>
@@ -1888,7 +1864,7 @@
       <c r="F11"/>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="32" t="s">
         <v>22</v>
       </c>
@@ -1903,7 +1879,7 @@
       <c r="F12"/>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="32" t="s">
         <v>12</v>
       </c>
@@ -1918,9 +1894,9 @@
       <c r="F13"/>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="40">
         <v>0</v>
@@ -1933,7 +1909,7 @@
       <c r="F14"/>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="32" t="s">
         <v>13</v>
       </c>
@@ -1948,9 +1924,9 @@
       <c r="F15"/>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="40">
         <v>0</v>
@@ -1963,7 +1939,7 @@
       <c r="F16"/>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
@@ -1972,7 +1948,7 @@
       <c r="F17"/>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18"/>
@@ -1981,7 +1957,7 @@
       <c r="F18"/>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19"/>
@@ -1990,7 +1966,7 @@
       <c r="F19"/>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20"/>
@@ -1999,7 +1975,7 @@
       <c r="F20"/>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
@@ -2008,7 +1984,7 @@
       <c r="F21"/>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -2017,7 +1993,7 @@
       <c r="F22"/>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -2025,7 +2001,7 @@
       <c r="F23"/>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -2033,7 +2009,7 @@
       <c r="F24"/>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -2041,7 +2017,7 @@
       <c r="F25"/>
       <c r="G25"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
@@ -2055,83 +2031,83 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="22.85546875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
+    <col min="2" max="4" width="22.83203125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
       <c r="D1" s="34"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
       <c r="D2" s="34"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="34"/>
       <c r="C4" s="34"/>
       <c r="D4" s="34"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
       <c r="C10" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>7</v>
       </c>
@@ -2143,7 +2119,7 @@
       </c>
       <c r="D11"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>8</v>
       </c>
@@ -2155,9 +2131,9 @@
       </c>
       <c r="D12"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="40">
         <v>0</v>
@@ -2167,7 +2143,7 @@
       </c>
       <c r="D13"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="35" t="s">
         <v>13</v>
       </c>
@@ -2179,9 +2155,9 @@
       </c>
       <c r="D14"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="40">
         <v>0</v>
@@ -2191,27 +2167,27 @@
       </c>
       <c r="D15"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20"/>
     </row>
   </sheetData>

--- a/ebegu-server/src/main/resources/reporting/Zahlungen_FR.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_FR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A1829-8AC6-4B44-BE78-6C52D3E1A31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A8C94B-73DC-404F-B8DE-CCFF30E2280F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="85" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>{periodeParam}</t>
   </si>
@@ -116,9 +116,6 @@
     <t>{kindNachname} {kindVorname}</t>
   </si>
   <si>
-    <t>Filter</t>
-  </si>
-  <si>
     <t>{bisParam}</t>
   </si>
   <si>
@@ -179,108 +176,7 @@
     <t>Titulaire du compte</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Versement à la structure d’accueil : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">montant versé par la commune à la structure d’accueil. Le montant comporte des corrections qui ont été reprises dans le cadre du cycle de paiement à la structure d’accueil. Il est déduit des </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>coûts com-plets dans la facture aux personnes requérantes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Décompte direct entre la commune et les personnes requé-rantes : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">montant corrigé par rapport au bon de garde effectif. Correspond à la différence entre le montant versé à la struc-ture d’accueil et le bon de garde en cours de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>validité. La commune verse ce montant corrigé directement aux per-sonnes requérantes, sans passer par kiBon.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bons de garde ayant donné lieu à une décision : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">montant du bon de garde par enfant et par mois selon la décision en cours de validité. Le montant inclut les corrections reprises dans le cycle de paiement avec la structure </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>d’accueil ainsi que les versements non repris dans ce cadre qui ont été décomptés directement entre la commune et les personnes requérantes.</t>
-    </r>
-  </si>
-  <si>
-    <t>filtrage</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bons de garde accordés </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Versement à la structure d’accueil :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> montant versé par la commune à la structure d’accueil. Le montant comporte des corrections qui ont été reprises dans le cadre du cycle de paiement à la structure d’accueil. Il est déduit des coûts com-plets dans la facture aux personnes requérantes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Décompte direct entre la commune et les personnes requé-rantes :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> montant corrigé par rapport au bon de garde effectif. Correspond à la différence entre le montant versé à la struc-ture d’accueil et le bon de garde en cours de validité. La commune verse ce montant corrigé directement aux per-sonnes requérantes, sans passer par kiBon.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -317,9 +213,6 @@
     <t>Versements</t>
   </si>
   <si>
-    <t>Paramètres</t>
-  </si>
-  <si>
     <t>Période</t>
   </si>
   <si>
@@ -332,12 +225,80 @@
     <t>Summe von Montant en francs</t>
   </si>
   <si>
-    <t>Versement à la structure d’accueil</t>
-  </si>
-  <si>
     <t>Cellule complétée</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Versement à la structure d’accueil :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> montant versé par la commune à la structure d’accueil. Le montant comporte des corrections qui ont été reprises dans le cadre du cycle de paiement à la structure d’accueil. Il est déduit des coûts complets dans la facture aux personnes requérantes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Décompte direct entre la commune et les personnes requérantes :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> montant corrigé par rapport au bon de garde effectif. Correspond à la différence entre le montant versé à la structure d’accueil et le bon de garde en cours de validité. La commune verse ce montant corrigé directement aux personnes requérantes, sans passer par kiBon.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Versement à la structure d’accueil : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>montant versé par la commune à la structure d’accueil. Le montant comporte des corrections qui ont été reprises dans le cadre du cycle de paiement à la structure d’accueil. Il est déduit des coûts complets dans la facture aux personnes requérantes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Décompte direct entre la commune et les personnes requérantes : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>montant corrigé par rapport au bon de garde effectif. Correspond à la différence entre le montant versé à la structure d’accueil et le bon de garde en cours de validité. La commune verse ce montant corrigé directement aux personnes requérantes, sans passer par kiBon.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bons de garde ayant donné lieu à une décision : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>montant du bon de garde par enfant et par mois selon la décision en cours de validité. Le montant inclut les corrections reprises dans le cycle de paiement avec la structure d’accueil ainsi que les versements non repris dans ce cadre qui ont été décomptés directement entre la commune et les personnes requérantes.</t>
+    </r>
+  </si>
+  <si>
     <t>Étiquettes de colonnes</t>
   </si>
   <si>
@@ -345,6 +306,12 @@
   </si>
   <si>
     <t>(Tous)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Filtrage</t>
+  </si>
+  <si>
+    <t>Décompte direct entre la commune et les personnes requérantes</t>
   </si>
 </sst>
 </file>
@@ -352,8 +319,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="165" formatCode="&quot;CHF &quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;CHF &quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -501,9 +468,9 @@
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -511,13 +478,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -527,15 +494,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -578,7 +544,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -593,7 +562,37 @@
     <cellStyle name="Pivot Table Value" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="53">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
     <dxf>
       <alignment wrapText="1" indent="0"/>
     </dxf>
@@ -617,6 +616,57 @@
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -636,6 +686,12 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -752,7 +808,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Kafader Simon" refreshedDate="46027.606349189817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{19CCD4CE-71BA-456C-AC09-85819591646C}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Nell Frédéric" refreshedDate="46092.52444108796" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="2" xr:uid="{19CCD4CE-71BA-456C-AC09-85819591646C}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A12:V1048576" sheet="Data"/>
   </cacheSource>
@@ -775,7 +831,7 @@
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Date de création du cycle de paiement" numFmtId="164">
+    <cacheField name="Date de création du cycle de paiement" numFmtId="22">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Nom de famille" numFmtId="0">
@@ -817,7 +873,7 @@
     <cacheField name="Taux de prise en charge subventionné" numFmtId="10">
       <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Montant en francs" numFmtId="165">
+    <cacheField name="Montant en francs" numFmtId="164">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Rectification" numFmtId="0">
@@ -839,15 +895,17 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Versement à (pour enfant tableau croisé dynamique)" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="Versement à la structure d’accueil"/>
+      <sharedItems containsBlank="1" count="3">
+        <s v="Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten"/>
         <m/>
+        <s v="Versement à la structure d’accueil" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Versement à  (pour commune tableau croisé dynamique)" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="Versement à la structure d’accueil"/>
+      <sharedItems containsBlank="1" count="3">
+        <s v="Ausserhalb von kiBon"/>
         <m/>
+        <s v="Versement à la structure d’accueil" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -878,7 +936,7 @@
     <s v="{bgPensum}"/>
     <s v="{betrag}"/>
     <s v="{korrektur}"/>
-    <s v="{ignorieren}"/>
+    <s v="x"/>
     <s v="{ibanEltern}"/>
     <s v="{kontoEltern}"/>
     <x v="0"/>
@@ -913,7 +971,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8E51875-8A88-48FE-A37D-3A132351B8AB}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="filtrage">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F8E51875-8A88-48FE-A37D-3A132351B8AB}" name="PivotTable1" cacheId="85" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption=" Filtrage">
   <location ref="A8:C16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
@@ -978,9 +1036,10 @@
       </items>
     </pivotField>
     <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
-      <items count="3">
-        <item x="0"/>
+      <items count="4">
+        <item m="1" x="2"/>
         <item x="1"/>
+        <item n="Décompte direct entre la commune et les personnes requérantes" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1022,7 +1081,7 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -1034,30 +1093,51 @@
   <dataFields count="1">
     <dataField name="Summe von Montant en francs" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="8">
-    <format dxfId="23">
+  <formats count="11">
+    <format dxfId="52">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="51">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="50">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="49">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="47">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="46">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="20" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="20">
+      <pivotArea grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="20" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -1070,7 +1150,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{182DBE84-424D-47FB-9F75-85364042AE94}" name="DataPilot1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{182DBE84-424D-47FB-9F75-85364042AE94}" name="DataPilot1" cacheId="85" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Bons de garde accordés " updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption=" Filtrage">
   <location ref="A9:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
@@ -1125,9 +1205,10 @@
     </pivotField>
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
     <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
-      <items count="3">
-        <item x="0"/>
+      <items count="4">
+        <item m="1" x="2"/>
         <item x="1"/>
+        <item n="Décompte direct entre la commune et les personnes requérantes" x="0"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1160,7 +1241,7 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -1172,15 +1253,57 @@
   <dataFields count="1">
     <dataField name="Summe von Montant en francs" fld="14" baseField="3" baseItem="0"/>
   </dataFields>
-  <formats count="3">
-    <format dxfId="15">
+  <formats count="9">
+    <format dxfId="44">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="43">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="41">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -1493,55 +1616,53 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="21" customWidth="1"/>
     <col min="3" max="4" width="21.1640625" customWidth="1"/>
     <col min="5" max="5" width="34.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.1640625" customWidth="1"/>
     <col min="9" max="9" width="21.1640625" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="22" customWidth="1"/>
-    <col min="11" max="11" width="11.1640625" style="22" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="22" customWidth="1"/>
-    <col min="13" max="13" width="19.5" style="22" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="21" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="21" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="21" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="21" customWidth="1"/>
     <col min="14" max="14" width="19.5" style="2" customWidth="1"/>
     <col min="15" max="15" width="16.5" style="3" customWidth="1"/>
     <col min="16" max="16" width="11.5" style="4"/>
     <col min="17" max="17" width="18.83203125" style="4" customWidth="1"/>
     <col min="18" max="19" width="23.33203125" customWidth="1"/>
-    <col min="20" max="20" width="21.1640625" customWidth="1"/>
-    <col min="21" max="21" width="44.33203125" customWidth="1"/>
-    <col min="22" max="22" width="47.5" style="4" customWidth="1"/>
+    <col min="20" max="20" width="21.1640625" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="44.33203125" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="47.5" style="4" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>56</v>
+      <c r="A1" s="38" t="s">
+        <v>49</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="A3" s="5"/>
       <c r="B3" s="18"/>
       <c r="T3" s="5"/>
       <c r="U3" s="5"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="39" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1549,107 +1670,107 @@
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="39" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="39" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>24</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:23" s="11" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="C12" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="J12" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="K12" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="L12" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="20" t="s">
+      <c r="M12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="20" t="s">
+      <c r="N12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="O12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="P12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="Q12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="Q12" s="10" t="s">
+      <c r="R12" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="R12" s="10" t="s">
+      <c r="S12" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="S12" s="10" t="s">
-        <v>43</v>
-      </c>
       <c r="T12" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -1674,10 +1795,10 @@
       <c r="I13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="K13" s="21" t="str">
+      <c r="K13" s="20" t="str">
         <f>TEXT(J13,"MMM")</f>
         <v>{zeitabschnittVon}</v>
       </c>
@@ -1685,7 +1806,7 @@
         <f>YEAR(J13)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="20" t="s">
         <v>14</v>
       </c>
       <c r="N13" s="14" t="s">
@@ -1729,12 +1850,12 @@
     <sortCondition ref="J13"/>
   </sortState>
   <conditionalFormatting sqref="A13:P13 R13:W13">
-    <cfRule type="expression" dxfId="12" priority="4">
+    <cfRule type="expression" dxfId="39" priority="4">
       <formula>$N13="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>$M13="X"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1748,66 +1869,66 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" style="26" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" style="26" customWidth="1"/>
-    <col min="9" max="16384" width="11.5" style="26"/>
+    <col min="1" max="1" width="26.83203125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="25" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" style="25" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="33"/>
+      <c r="A1" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="2" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="33"/>
+      <c r="A2" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="32"/>
     </row>
     <row r="3" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="33"/>
+      <c r="A3" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="32"/>
     </row>
     <row r="4" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="33"/>
+      <c r="A4" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="31"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>66</v>
+      <c r="A6" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1815,23 +1936,23 @@
       <c r="F7"/>
     </row>
     <row r="8" spans="1:7" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="27" t="s">
+      <c r="A8" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D8"/>
-    </row>
-    <row r="9" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>48</v>
+      <c r="C9" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -1839,7 +1960,7 @@
       <c r="G9"/>
     </row>
     <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="31" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="40"/>
@@ -1850,7 +1971,7 @@
       <c r="G10"/>
     </row>
     <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="40">
@@ -1865,7 +1986,7 @@
       <c r="G11"/>
     </row>
     <row r="12" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="40">
@@ -1880,7 +2001,7 @@
       <c r="G12"/>
     </row>
     <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="31" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="40">
@@ -1895,8 +2016,8 @@
       <c r="G13"/>
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="32" t="s">
-        <v>65</v>
+      <c r="A14" s="31" t="s">
+        <v>61</v>
       </c>
       <c r="B14" s="40">
         <v>0</v>
@@ -1910,7 +2031,7 @@
       <c r="G14"/>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="40">
@@ -1925,8 +2046,8 @@
       <c r="G15"/>
     </row>
     <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="32" t="s">
-        <v>48</v>
+      <c r="A16" s="31" t="s">
+        <v>43</v>
       </c>
       <c r="B16" s="40">
         <v>0</v>
@@ -2025,6 +2146,37 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <cellWatches>
+    <cellWatch r="A6"/>
+    <cellWatch r="B6"/>
+    <cellWatch r="A8"/>
+    <cellWatch r="B8"/>
+    <cellWatch r="C8"/>
+    <cellWatch r="A9"/>
+    <cellWatch r="B9"/>
+    <cellWatch r="C9"/>
+    <cellWatch r="A10"/>
+    <cellWatch r="B10"/>
+    <cellWatch r="C10"/>
+    <cellWatch r="A11"/>
+    <cellWatch r="B11"/>
+    <cellWatch r="C11"/>
+    <cellWatch r="A12"/>
+    <cellWatch r="B12"/>
+    <cellWatch r="C12"/>
+    <cellWatch r="A13"/>
+    <cellWatch r="B13"/>
+    <cellWatch r="C13"/>
+    <cellWatch r="A14"/>
+    <cellWatch r="B14"/>
+    <cellWatch r="C14"/>
+    <cellWatch r="A15"/>
+    <cellWatch r="B15"/>
+    <cellWatch r="C15"/>
+    <cellWatch r="A16"/>
+    <cellWatch r="B16"/>
+    <cellWatch r="C16"/>
+  </cellWatches>
 </worksheet>
 </file>
 
@@ -2034,7 +2186,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="22.83203125" style="26" customWidth="1"/>
+    <col min="2" max="4" width="22.83203125" style="25" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
@@ -2042,68 +2194,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="A1" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="A2" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="A3" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
+      <c r="A4" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="23" t="s">
-        <v>63</v>
+      <c r="A7" s="22" t="s">
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="23" t="s">
+      <c r="A9" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D9"/>
-    </row>
-    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>48</v>
+      <c r="C10" s="25" t="s">
+        <v>43</v>
       </c>
       <c r="D10"/>
     </row>
@@ -2120,7 +2272,7 @@
       <c r="D11"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="40">
@@ -2132,8 +2284,8 @@
       <c r="D12"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
-        <v>65</v>
+      <c r="A13" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="B13" s="40">
         <v>0</v>
@@ -2144,7 +2296,7 @@
       <c r="D13"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="34" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="40">
@@ -2155,9 +2307,9 @@
       </c>
       <c r="D14"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>48</v>
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="31" t="s">
+        <v>43</v>
       </c>
       <c r="B15" s="40">
         <v>0</v>
